--- a/report/downloads/reports/网点变化对比报告_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="减少网点（46家）" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="C12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>-100.0%</t>
+      <c r="C12" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,14 @@
         <v>8626</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8612</v>
+        <v>8630</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6332,297 +6332,297 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="inlineStr">
+      <c r="A259" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B259" s="3" t="inlineStr">
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>云南</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D260" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E260" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D262" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E262" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D263" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D264" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D266" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
         <is>
           <t>浙江</t>
         </is>
       </c>
-      <c r="C259" s="3" t="n">
+      <c r="C267" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D259" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E259" s="3" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="3" t="inlineStr">
+      <c r="D267" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B260" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C260" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D260" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E260" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="3" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E268" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B261" s="3" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C261" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D261" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E261" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="3" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E269" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B262" s="3" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C262" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D262" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="3" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>福建</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D270" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E270" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B263" s="3" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C263" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D263" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E263" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="3" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B264" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C264" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D264" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E264" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="C265" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D265" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E265" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C266" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D266" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E266" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B267" s="3" t="inlineStr">
-        <is>
-          <t>山东</t>
-        </is>
-      </c>
-      <c r="C267" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D267" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E267" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="C268" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D268" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E268" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="C269" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D269" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E269" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B270" s="3" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="C270" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D270" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E270" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B271" s="3" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="C271" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D271" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E271" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B272" s="3" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
         <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E272" s="3" t="n">
-        <v>-1</v>
+      <c r="C272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -10950,7 +10950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -11388,842 +11388,356 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>意特汽车商业（上海）有限公司</t>
+          <t>深圳坪山益田假日广场</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>恒通东路69号101单元 龙盛福新汇 上海 上海</t>
+          <t>广东省深圳市坪山区坪山街道六联社区深汕路（坪山段）168号益田假日世界中庭CT-L1-05号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>昆明乐骏汽车销售服务有限公司</t>
+          <t>南昌红谷滩万达广场体验店</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>昆明市</t>
+          <t>南昌市</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>滇池度假区滇池路1103号平安大厦B座1层 平安大厦 昆明市 滇池度假区</t>
+          <t>江西省南昌市红谷滩新区会展路999号万达广场</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>北京骏东汽车销售服务有限公司</t>
+          <t>理想汽车银川悠阅城零售中心</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>银川市</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>金宝街 金宝大厦一层 北京 东城区</t>
+          <t>宁夏回族自治区银川市金凤区正源南街与凤仪路交会处悠阅城1号楼1层128号商铺</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>成都骏意汽车销售服务有限公司</t>
+          <t>理想汽车东莞长安万达零售中心</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>成都市</t>
+          <t>东莞市</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>成都市高新区火车南站西路 法拉利 成都市 中国</t>
+          <t>广东省东莞市长安镇霄边社区东门中路1号长安万达广场2号门1007室</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>安徽鸿粤鸿超汽车销售服务有限公司</t>
+          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>合肥市</t>
+          <t>伊犁</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>花亭湖路与齐云山路交叉口 安徽鸿粤鸿超汽车销售服务有限公司 合肥 蜀山区</t>
+          <t>新疆伊犁哈萨克自治州伊宁市巴彦岱镇三段村资源路1号伊宁城投汽车产业园一号展厅东侧二楼202室</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>青岛恒骏汽车销售服务有限公司</t>
+          <t>理想汽车毕节双山国际汽车城授权钣喷中心（荣信店）</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>青岛市</t>
+          <t>毕节市</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>青岛市市南区东海西路1号1号楼丙户 青岛市 市南区</t>
+          <t>贵州省毕节市七星关区响水乡吊兰社区小瓦路8号双山国际汽车城1-1号商铺</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>广东骏佳汽车服务有限公司</t>
+          <t>理想汽车贵阳花溪临时交付中心</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>广州市</t>
+          <t>贵阳市</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>天河区珠江新城清风街1-48号 新世界广场首层 Guangzhou</t>
+          <t>贵阳市花溪区孟关乡孟关村 A-22</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>骏佳行汽车服务（深圳）有限公司</t>
+          <t>理想汽车大连华南万象汇零售中心</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>大连市</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>中心路1号 深圳湾壹号北区2栋 Shenzhen Nanshan District</t>
+          <t>辽宁省大连市甘井子区山东路 350 号、352 号 华润置地 大连华南万象汇 的 LG203</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>南京瑞骏汽车销售服务有限公司</t>
+          <t>阿斯顿·马丁北京</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>南京市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>长江路100号 长江会 南京 玄武</t>
+          <t>东城区金宝街99号 , 北京, 100005</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>苏州意骏汽车销售服务有限公司</t>
+          <t>阿斯顿·马丁北京售后服务中心</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>苏州工业园区思安街99号协鑫广场西侧1F Suzhou</t>
+          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>宁波骏意汽车服务有限公司</t>
+          <t>鸿蒙智行尚界用户中心•运城机场大道</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>宁波市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>中官新路 A号楼 Ningbo Jiangbei District</t>
+          <t>山西省运城市盐湖区机场大道与库东路交叉口西南160米</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>杭州骏意汽车销售服务有限公司</t>
+          <t>华为智能生活馆•邢台逗号立方</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>杭州市</t>
+          <t>邢台市</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>浙江省杭州市南山路 杭州 上城区</t>
+          <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>温州骏意汽车服务有限公司</t>
+          <t>华为智能生活馆•武汉经开永旺梦乐城</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>武汉市</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>温州经济技术开发区滨海园区 3号4S店东侧 温州 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>武汉骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>解放大道634号K11步行街 108-109 武汉 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>长沙市骏马汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>长沙市</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>潇湘北路 圆泰长沙印 103-1 号 长沙市 中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>福建骏佳行汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>福建</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>厦门市</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>环岛东路1821号 中航紫金广场商业街 厦门市 思明区</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>重庆骏东汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>重庆两江新区新南路 龙湖晶郦馆A栋-1F-03b Chongqing New South St</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>西安丽骏汽车销售服务有限公司</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>陕西</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>西安市</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>锦业二路 高新贝多产业园 Xi'an High-tech Zone</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>深圳坪山益田假日广场</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>深圳市</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>广东省深圳市坪山区坪山街道六联社区深汕路（坪山段）168号益田假日世界中庭CT-L1-05号</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>南昌红谷滩万达广场体验店</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>江西</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>南昌市</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>江西省南昌市红谷滩新区会展路999号万达广场</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车银川悠阅城零售中心</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>银川市</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>宁夏回族自治区银川市金凤区正源南街与凤仪路交会处悠阅城1号楼1层128号商铺</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车东莞长安万达零售中心</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>东莞市</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>广东省东莞市长安镇霄边社区东门中路1号长安万达广场2号门1007室</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车伊犁伊宁授权钣喷中心（鑫海新星店）</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>伊犁</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>新疆伊犁哈萨克自治州伊宁市巴彦岱镇三段村资源路1号伊宁城投汽车产业园一号展厅东侧二楼202室</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车毕节双山国际汽车城授权钣喷中心（荣信店）</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>毕节市</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>贵州省毕节市七星关区响水乡吊兰社区小瓦路8号双山国际汽车城1-1号商铺</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车贵阳花溪临时交付中心</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>贵阳市</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>贵阳市花溪区孟关乡孟关村 A-22</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>理想汽车大连华南万象汇零售中心</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>大连市</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>辽宁省大连市甘井子区山东路 350 号、352 号 华润置地 大连华南万象汇 的 LG203</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁北京售后服务中心</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>大兴区金时大街7号院5号楼, 北京, 100076</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁北京</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>东城区金宝街99号 , 北京, 100005</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行尚界用户中心•运城机场大道</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>运城市</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>山西省运城市盐湖区机场大道与库东路交叉口西南160米</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•邢台逗号立方</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>邢台市</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>河北省邢台市信都区中兴西大街逗号立方购物公园1F</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•武汉经开永旺梦乐城</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>武汉市</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>武汉经济技术开发区江城大道永旺梦乐城NO.B113b</t>
         </is>
@@ -12286,22 +11800,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -12311,29 +11825,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -12343,29 +11857,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -12375,29 +11889,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12407,29 +11921,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12439,29 +11953,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12471,7 +11985,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12483,17 +11997,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12503,29 +12017,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12535,7 +12049,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
@@ -12547,17 +12061,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12567,29 +12081,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12599,29 +12113,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12631,14 +12145,14 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -12648,12 +12162,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12663,29 +12177,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12695,29 +12209,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12727,29 +12241,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12759,29 +12273,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12791,29 +12305,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12823,29 +12337,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12855,29 +12369,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12887,29 +12401,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12919,29 +12433,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12951,7 +12465,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -12990,22 +12504,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13022,22 +12536,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13054,22 +12568,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13091,17 +12605,17 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13182,22 +12696,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -13207,29 +12721,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -13239,7 +12753,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（34家）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="C12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -875,14 +875,14 @@
         <v>8626</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>8630</v>
+        <v>8632</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6626,66 +6626,66 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="inlineStr">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D273" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D274" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
         <is>
           <t>特斯拉</t>
         </is>
       </c>
-      <c r="B273" s="3" t="inlineStr">
+      <c r="B275" s="3" t="inlineStr">
         <is>
           <t>江西</t>
         </is>
       </c>
-      <c r="C273" s="3" t="n">
+      <c r="C275" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="D273" s="3" t="n">
+      <c r="D275" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E273" s="3" t="n">
+      <c r="E275" s="3" t="n">
         <v>-1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="D274" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="E274" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D275" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E275" s="2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -6696,14 +6696,14 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C276" s="2" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="D276" s="2" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="E276" s="2" t="n">
         <v>0</v>
@@ -6717,14 +6717,14 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D277" s="2" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E277" s="2" t="n">
         <v>0</v>
@@ -6738,14 +6738,14 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C278" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E278" s="2" t="n">
         <v>0</v>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C279" s="2" t="n">
@@ -6780,14 +6780,14 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D280" s="2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E280" s="2" t="n">
         <v>0</v>
@@ -6801,14 +6801,14 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E281" s="2" t="n">
         <v>0</v>
@@ -6822,14 +6822,14 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E282" s="2" t="n">
         <v>0</v>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D283" s="2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E283" s="2" t="n">
         <v>0</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C284" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D284" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E284" s="2" t="n">
         <v>0</v>
@@ -6885,14 +6885,14 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E285" s="2" t="n">
         <v>0</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="E286" s="2" t="n">
         <v>0</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E287" s="2" t="n">
         <v>0</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D288" s="2" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E288" s="2" t="n">
         <v>0</v>
@@ -6969,14 +6969,14 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="E289" s="2" t="n">
         <v>0</v>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E290" s="2" t="n">
         <v>0</v>
@@ -7011,14 +7011,14 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="D291" s="2" t="n">
-        <v>18</v>
+        <v>88</v>
       </c>
       <c r="E291" s="2" t="n">
         <v>0</v>
@@ -7032,14 +7032,14 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E292" s="2" t="n">
         <v>0</v>
@@ -7053,14 +7053,14 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E293" s="2" t="n">
         <v>0</v>
@@ -7074,14 +7074,14 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E294" s="2" t="n">
         <v>0</v>
@@ -7095,14 +7095,14 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D295" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E295" s="2" t="n">
         <v>0</v>
@@ -7116,14 +7116,14 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D296" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E296" s="2" t="n">
         <v>0</v>
@@ -7137,14 +7137,14 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C297" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D297" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E297" s="2" t="n">
         <v>0</v>
@@ -7158,14 +7158,14 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D298" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E298" s="2" t="n">
         <v>0</v>
@@ -7179,59 +7179,59 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D299" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D300" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E300" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C299" s="2" t="n">
+      <c r="C301" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D299" s="2" t="n">
+      <c r="D301" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E299" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>广东</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="D300" s="4" t="n">
-        <v>84</v>
-      </c>
-      <c r="E300" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>特斯拉</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>新疆</t>
-        </is>
-      </c>
-      <c r="C301" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D301" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E301" s="4" t="n">
-        <v>1</v>
+      <c r="E301" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -7242,59 +7242,59 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="D302" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="E302" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D303" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E303" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>特斯拉</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="C302" s="4" t="n">
+      <c r="C304" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D302" s="4" t="n">
+      <c r="D304" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="E302" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B303" s="3" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="C303" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="D303" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="E303" s="3" t="n">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="inlineStr">
-        <is>
-          <t>理想</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="inlineStr">
-        <is>
-          <t>宁夏</t>
-        </is>
-      </c>
-      <c r="C304" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D304" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E304" s="3" t="n">
-        <v>-1</v>
+      <c r="E304" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -7305,17 +7305,17 @@
       </c>
       <c r="B305" s="3" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C305" s="3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D305" s="3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E305" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="306">
@@ -7326,59 +7326,59 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C306" s="3" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E306" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="inlineStr">
+      <c r="A307" s="3" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B307" s="2" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C307" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="D307" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E307" s="2" t="n">
-        <v>0</v>
+      <c r="B307" s="3" t="inlineStr">
+        <is>
+          <t>新疆</t>
+        </is>
+      </c>
+      <c r="C307" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="inlineStr">
+      <c r="A308" s="3" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B308" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C308" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="D308" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="E308" s="2" t="n">
-        <v>0</v>
+      <c r="B308" s="3" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C308" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="309">
@@ -7389,14 +7389,14 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D309" s="2" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E309" s="2" t="n">
         <v>0</v>
@@ -7410,14 +7410,14 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D310" s="2" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E310" s="2" t="n">
         <v>0</v>
@@ -7431,14 +7431,14 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E311" s="2" t="n">
         <v>0</v>
@@ -7452,14 +7452,14 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C312" s="2" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D312" s="2" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E312" s="2" t="n">
         <v>0</v>
@@ -7473,14 +7473,14 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D313" s="2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E313" s="2" t="n">
         <v>0</v>
@@ -7494,14 +7494,14 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="E314" s="2" t="n">
         <v>0</v>
@@ -7515,14 +7515,14 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E315" s="2" t="n">
         <v>0</v>
@@ -7536,14 +7536,14 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="D316" s="2" t="n">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="E316" s="2" t="n">
         <v>0</v>
@@ -7557,14 +7557,14 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E317" s="2" t="n">
         <v>0</v>
@@ -7578,14 +7578,14 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="E318" s="2" t="n">
         <v>0</v>
@@ -7599,14 +7599,14 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D319" s="2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E319" s="2" t="n">
         <v>0</v>
@@ -7620,14 +7620,14 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C320" s="2" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="D320" s="2" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="E320" s="2" t="n">
         <v>0</v>
@@ -7641,14 +7641,14 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="E321" s="2" t="n">
         <v>0</v>
@@ -7662,14 +7662,14 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="E322" s="2" t="n">
         <v>0</v>
@@ -7683,14 +7683,14 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="E323" s="2" t="n">
         <v>0</v>
@@ -7704,14 +7704,14 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="D324" s="2" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E324" s="2" t="n">
         <v>0</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E325" s="2" t="n">
         <v>0</v>
@@ -7746,14 +7746,14 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="E326" s="2" t="n">
         <v>0</v>
@@ -7767,14 +7767,14 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D327" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E327" s="2" t="n">
         <v>0</v>
@@ -7788,14 +7788,14 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E328" s="2" t="n">
         <v>0</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C329" s="2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D329" s="2" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E329" s="2" t="n">
         <v>0</v>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C330" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D330" s="2" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E330" s="2" t="n">
         <v>0</v>
@@ -7851,14 +7851,14 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C331" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D331" s="2" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E331" s="2" t="n">
         <v>0</v>
@@ -7872,80 +7872,80 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C332" s="2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D332" s="2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E332" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="4" t="inlineStr">
+      <c r="A333" s="2" t="inlineStr">
         <is>
           <t>理想</t>
         </is>
       </c>
-      <c r="B333" s="4" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="C333" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="D333" s="4" t="n">
-        <v>46</v>
-      </c>
-      <c r="E333" s="4" t="n">
-        <v>1</v>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D333" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E333" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>蔚来</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C334" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D334" s="2" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E334" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="inlineStr">
-        <is>
-          <t>蔚来</t>
-        </is>
-      </c>
-      <c r="B335" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C335" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="D335" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E335" s="2" t="n">
-        <v>0</v>
+      <c r="A335" s="4" t="inlineStr">
+        <is>
+          <t>理想</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="D335" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="E335" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -7956,14 +7956,14 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C336" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D336" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E336" s="2" t="n">
         <v>0</v>
@@ -7977,14 +7977,14 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C337" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D337" s="2" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E337" s="2" t="n">
         <v>0</v>
@@ -7998,14 +7998,14 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C338" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D338" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E338" s="2" t="n">
         <v>0</v>
@@ -8019,14 +8019,14 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C339" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D339" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E339" s="2" t="n">
         <v>0</v>
@@ -8040,14 +8040,14 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C340" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D340" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E340" s="2" t="n">
         <v>0</v>
@@ -8061,14 +8061,14 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C341" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D341" s="2" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E341" s="2" t="n">
         <v>0</v>
@@ -8082,14 +8082,14 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C342" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D342" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E342" s="2" t="n">
         <v>0</v>
@@ -8103,14 +8103,14 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C343" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D343" s="2" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E343" s="2" t="n">
         <v>0</v>
@@ -8124,14 +8124,14 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C344" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D344" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E344" s="2" t="n">
         <v>0</v>
@@ -8145,14 +8145,14 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C345" s="2" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="D345" s="2" t="n">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="E345" s="2" t="n">
         <v>0</v>
@@ -8166,14 +8166,14 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C346" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D346" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E346" s="2" t="n">
         <v>0</v>
@@ -8187,14 +8187,14 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C347" s="2" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D347" s="2" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E347" s="2" t="n">
         <v>0</v>
@@ -8208,14 +8208,14 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C348" s="2" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="D348" s="2" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="E348" s="2" t="n">
         <v>0</v>
@@ -8229,14 +8229,14 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C349" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D349" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E349" s="2" t="n">
         <v>0</v>
@@ -8250,14 +8250,14 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C350" s="2" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="D350" s="2" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="E350" s="2" t="n">
         <v>0</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C351" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D351" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E351" s="2" t="n">
         <v>0</v>
@@ -8292,14 +8292,14 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C352" s="2" t="n">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="D352" s="2" t="n">
-        <v>87</v>
+        <v>13</v>
       </c>
       <c r="E352" s="2" t="n">
         <v>0</v>
@@ -8313,14 +8313,14 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C353" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D353" s="2" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E353" s="2" t="n">
         <v>0</v>
@@ -8334,14 +8334,14 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C354" s="2" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="D354" s="2" t="n">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="E354" s="2" t="n">
         <v>0</v>
@@ -8355,14 +8355,14 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C355" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D355" s="2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E355" s="2" t="n">
         <v>0</v>
@@ -8376,14 +8376,14 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C356" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D356" s="2" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E356" s="2" t="n">
         <v>0</v>
@@ -8397,14 +8397,14 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C357" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D357" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E357" s="2" t="n">
         <v>0</v>
@@ -8418,14 +8418,14 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C358" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D358" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E358" s="2" t="n">
         <v>0</v>
@@ -8439,14 +8439,14 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C359" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D359" s="2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E359" s="2" t="n">
         <v>0</v>
@@ -8460,14 +8460,14 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C360" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D360" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E360" s="2" t="n">
         <v>0</v>
@@ -8481,14 +8481,14 @@
       </c>
       <c r="B361" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C361" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D361" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E361" s="2" t="n">
         <v>0</v>
@@ -8502,14 +8502,14 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C362" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D362" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E362" s="2" t="n">
         <v>0</v>
@@ -8523,49 +8523,49 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C363" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D363" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E363" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="3" t="inlineStr">
-        <is>
-          <t>阿斯顿·马丁</t>
-        </is>
-      </c>
-      <c r="B364" s="3" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C364" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D364" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E364" s="3" t="n">
-        <v>-2</v>
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>蔚来</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D364" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E364" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>蔚来</t>
         </is>
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C365" s="2" t="n">
@@ -8579,24 +8579,24 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="inlineStr">
+      <c r="A366" s="3" t="inlineStr">
         <is>
           <t>阿斯顿·马丁</t>
         </is>
       </c>
-      <c r="B366" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C366" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D366" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E366" s="2" t="n">
-        <v>0</v>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="C366" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D366" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E366" s="3" t="n">
+        <v>-2</v>
       </c>
     </row>
     <row r="367">
@@ -8607,14 +8607,14 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C367" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D367" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367" s="2" t="n">
         <v>0</v>
@@ -8628,14 +8628,14 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C368" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D368" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E368" s="2" t="n">
         <v>0</v>
@@ -8649,14 +8649,14 @@
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C369" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D369" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E369" s="2" t="n">
         <v>0</v>
@@ -8670,14 +8670,14 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C370" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D370" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E370" s="2" t="n">
         <v>0</v>
@@ -8691,14 +8691,14 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C371" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D371" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E371" s="2" t="n">
         <v>0</v>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C372" s="2" t="n">
@@ -8726,66 +8726,66 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="inlineStr">
+      <c r="A373" s="2" t="inlineStr">
         <is>
           <t>阿斯顿·马丁</t>
         </is>
       </c>
-      <c r="B373" s="4" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="C373" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D373" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E373" s="4" t="n">
-        <v>1</v>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D373" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E373" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>雷克萨斯</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D374" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E374" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="inlineStr">
-        <is>
-          <t>雷克萨斯</t>
-        </is>
-      </c>
-      <c r="B375" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C375" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D375" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E375" s="2" t="n">
-        <v>0</v>
+      <c r="A375" s="4" t="inlineStr">
+        <is>
+          <t>阿斯顿·马丁</t>
+        </is>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D375" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E375" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -8796,14 +8796,14 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D376" s="2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E376" s="2" t="n">
         <v>0</v>
@@ -8817,14 +8817,14 @@
       </c>
       <c r="B377" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D377" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E377" s="2" t="n">
         <v>0</v>
@@ -8838,14 +8838,14 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D378" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E378" s="2" t="n">
         <v>0</v>
@@ -8859,14 +8859,14 @@
       </c>
       <c r="B379" s="2" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D379" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E379" s="2" t="n">
         <v>0</v>
@@ -8880,14 +8880,14 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C380" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D380" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E380" s="2" t="n">
         <v>0</v>
@@ -8901,14 +8901,14 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D381" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E381" s="2" t="n">
         <v>0</v>
@@ -8922,14 +8922,14 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C382" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D382" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E382" s="2" t="n">
         <v>0</v>
@@ -8943,14 +8943,14 @@
       </c>
       <c r="B383" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D383" s="2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E383" s="2" t="n">
         <v>0</v>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D384" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E384" s="2" t="n">
         <v>0</v>
@@ -8985,14 +8985,14 @@
       </c>
       <c r="B385" s="2" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C385" s="2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D385" s="2" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E385" s="2" t="n">
         <v>0</v>
@@ -9006,14 +9006,14 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D386" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E386" s="2" t="n">
         <v>0</v>
@@ -9027,14 +9027,14 @@
       </c>
       <c r="B387" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C387" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D387" s="2" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E387" s="2" t="n">
         <v>0</v>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="D388" s="2" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E388" s="2" t="n">
         <v>0</v>
@@ -9069,14 +9069,14 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D389" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E389" s="2" t="n">
         <v>0</v>
@@ -9090,14 +9090,14 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D390" s="2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E390" s="2" t="n">
         <v>0</v>
@@ -9111,14 +9111,14 @@
       </c>
       <c r="B391" s="2" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D391" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E391" s="2" t="n">
         <v>0</v>
@@ -9132,14 +9132,14 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D392" s="2" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E392" s="2" t="n">
         <v>0</v>
@@ -9153,14 +9153,14 @@
       </c>
       <c r="B393" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D393" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E393" s="2" t="n">
         <v>0</v>
@@ -9174,14 +9174,14 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D394" s="2" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E394" s="2" t="n">
         <v>0</v>
@@ -9195,14 +9195,14 @@
       </c>
       <c r="B395" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D395" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" s="2" t="n">
         <v>0</v>
@@ -9216,14 +9216,14 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D396" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E396" s="2" t="n">
         <v>0</v>
@@ -9237,14 +9237,14 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D397" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E397" s="2" t="n">
         <v>0</v>
@@ -9258,14 +9258,14 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D398" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E398" s="2" t="n">
         <v>0</v>
@@ -9279,14 +9279,14 @@
       </c>
       <c r="B399" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D399" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E399" s="2" t="n">
         <v>0</v>
@@ -9300,7 +9300,7 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C400" s="2" t="n">
@@ -9321,14 +9321,14 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D401" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E401" s="2" t="n">
         <v>0</v>
@@ -9342,14 +9342,14 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="C402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D402" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E402" s="2" t="n">
         <v>0</v>
@@ -9363,59 +9363,59 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D403" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E403" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D404" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E404" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>雷克萨斯</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C403" s="2" t="n">
+      <c r="C405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D403" s="2" t="n">
+      <c r="D405" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E403" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B404" s="3" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="C404" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="D404" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="E404" s="3" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="3" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B405" s="3" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="C405" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="D405" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="E405" s="3" t="n">
-        <v>-1</v>
+      <c r="E405" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="406">
@@ -9426,59 +9426,59 @@
       </c>
       <c r="B406" s="3" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C406" s="3" t="n">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D406" s="3" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E406" s="3" t="n">
         <v>-1</v>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="inlineStr">
+      <c r="A407" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B407" s="2" t="inlineStr">
-        <is>
-          <t>云南</t>
-        </is>
-      </c>
-      <c r="C407" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="D407" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="E407" s="2" t="n">
-        <v>0</v>
+      <c r="B407" s="3" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="C407" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="inlineStr">
+      <c r="A408" s="3" t="inlineStr">
         <is>
           <t>鸿蒙智行</t>
         </is>
       </c>
-      <c r="B408" s="2" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="C408" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="D408" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="E408" s="2" t="n">
-        <v>0</v>
+      <c r="B408" s="3" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="C408" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="409">
@@ -9489,14 +9489,14 @@
       </c>
       <c r="B409" s="2" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C409" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D409" s="2" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E409" s="2" t="n">
         <v>0</v>
@@ -9510,14 +9510,14 @@
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D410" s="2" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E410" s="2" t="n">
         <v>0</v>
@@ -9531,14 +9531,14 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D411" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E411" s="2" t="n">
         <v>0</v>
@@ -9552,14 +9552,14 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D412" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E412" s="2" t="n">
         <v>0</v>
@@ -9573,14 +9573,14 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D413" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E413" s="2" t="n">
         <v>0</v>
@@ -9594,14 +9594,14 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D414" s="2" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E414" s="2" t="n">
         <v>0</v>
@@ -9615,14 +9615,14 @@
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D415" s="2" t="n">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="E415" s="2" t="n">
         <v>0</v>
@@ -9636,14 +9636,14 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D416" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E416" s="2" t="n">
         <v>0</v>
@@ -9657,14 +9657,14 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D417" s="2" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E417" s="2" t="n">
         <v>0</v>
@@ -9678,14 +9678,14 @@
       </c>
       <c r="B418" s="2" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="D418" s="2" t="n">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="E418" s="2" t="n">
         <v>0</v>
@@ -9699,14 +9699,14 @@
       </c>
       <c r="B419" s="2" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="D419" s="2" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="E419" s="2" t="n">
         <v>0</v>
@@ -9720,59 +9720,59 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
+          <t>陕西</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="D420" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="E420" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>青海</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D421" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E421" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
           <t>黑龙江</t>
         </is>
       </c>
-      <c r="C420" s="2" t="n">
+      <c r="C422" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="D420" s="2" t="n">
+      <c r="D422" s="2" t="n">
         <v>22</v>
       </c>
-      <c r="E420" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B421" s="4" t="inlineStr">
-        <is>
-          <t>上海</t>
-        </is>
-      </c>
-      <c r="C421" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="D421" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="E421" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B422" s="4" t="inlineStr">
-        <is>
-          <t>内蒙古</t>
-        </is>
-      </c>
-      <c r="C422" s="4" t="n">
-        <v>34</v>
-      </c>
-      <c r="D422" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="E422" s="4" t="n">
-        <v>1</v>
+      <c r="E422" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="423">
@@ -9783,14 +9783,14 @@
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C423" s="4" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D423" s="4" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="E423" s="4" t="n">
         <v>1</v>
@@ -9804,14 +9804,14 @@
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C424" s="4" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D424" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E424" s="4" t="n">
         <v>1</v>
@@ -9825,14 +9825,14 @@
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C425" s="4" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="D425" s="4" t="n">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="E425" s="4" t="n">
         <v>1</v>
@@ -9846,14 +9846,14 @@
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C426" s="4" t="n">
-        <v>205</v>
+        <v>22</v>
       </c>
       <c r="D426" s="4" t="n">
-        <v>206</v>
+        <v>23</v>
       </c>
       <c r="E426" s="4" t="n">
         <v>1</v>
@@ -9867,14 +9867,14 @@
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C427" s="4" t="n">
-        <v>142</v>
+        <v>13</v>
       </c>
       <c r="D427" s="4" t="n">
-        <v>143</v>
+        <v>14</v>
       </c>
       <c r="E427" s="4" t="n">
         <v>1</v>
@@ -9888,14 +9888,14 @@
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C428" s="4" t="n">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="D428" s="4" t="n">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="E428" s="4" t="n">
         <v>1</v>
@@ -9909,14 +9909,14 @@
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C429" s="4" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="D429" s="4" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E429" s="4" t="n">
         <v>1</v>
@@ -9930,14 +9930,14 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C430" s="4" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="D430" s="4" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="E430" s="4" t="n">
         <v>1</v>
@@ -9951,14 +9951,14 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C431" s="4" t="n">
-        <v>39</v>
+        <v>151</v>
       </c>
       <c r="D431" s="4" t="n">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="E431" s="4" t="n">
         <v>1</v>
@@ -9972,14 +9972,14 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C432" s="4" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="D432" s="4" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="E432" s="4" t="n">
         <v>1</v>
@@ -9993,17 +9993,17 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C433" s="4" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="D433" s="4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E433" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -10014,16 +10014,58 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C434" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="D434" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="E434" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="C435" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D435" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E435" s="4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B436" s="4" t="inlineStr">
+        <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="C434" s="4" t="n">
+      <c r="C436" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="D434" s="4" t="n">
+      <c r="D436" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="E434" s="4" t="n">
+      <c r="E436" s="4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10038,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10321,54 +10363,54 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店L123</t>
+          <t>郑州悦骏汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
+          <t>如意西路 中国平煤神马集团 郑州 郑东新区</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>法拉利</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>茂名茂悦东荟城城市展厅L1-1292</t>
+          <t>沈阳鸿粤鸿福汽车销售服务有限公司</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>茂名市</t>
+          <t>沈阳市</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
+          <t>浑南区全运路 Shenyang China</t>
         </is>
       </c>
     </row>
@@ -10380,22 +10422,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>库尔勒汇嘉时代</t>
+          <t>深圳福田卓悦中心体验店L123</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
+          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
         </is>
       </c>
     </row>
@@ -10407,157 +10449,157 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>莆田城厢万达广场</t>
+          <t>茂名茂悦东荟城城市展厅L1-1292</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>莆田市</t>
+          <t>茂名市</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
+          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>理想汽车芜湖祥盛路零售中心</t>
+          <t>库尔勒汇嘉时代</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
+          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>理想汽车江门蓬江临时交付中心</t>
+          <t>莆田城厢万达广场</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>江门市</t>
+          <t>莆田市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路54号</t>
+          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁苏州</t>
+          <t>理想汽车芜湖祥盛路零售中心</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
+          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（宜家荟聚）</t>
+          <t>理想汽车江门蓬江临时交付中心</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江门市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>上海市长宁区金钟路788号01C04A 华为</t>
+          <t>江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>阿斯顿·马丁苏州</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
         </is>
       </c>
     </row>
@@ -10569,22 +10611,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>华为授权体验店（宜家荟聚）</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>上海市长宁区金钟路788号01C04A 华为</t>
         </is>
       </c>
     </row>
@@ -10596,22 +10638,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•天津西青大寺汽车园</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>天津市西青区大寺镇储源道17号</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
         </is>
       </c>
     </row>
@@ -10623,22 +10665,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•固原九龙路</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>固原市</t>
+          <t>眉山市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
@@ -10650,22 +10692,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（八佰伴）</t>
+          <t>AITO授权用户中心•天津西青大寺汽车园</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
+          <t>天津市西青区大寺镇储源道17号</t>
         </is>
       </c>
     </row>
@@ -10677,22 +10719,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>鸿蒙智行授权用户中心•固原九龙路</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>固原市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
         </is>
       </c>
     </row>
@@ -10704,22 +10746,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>华为授权体验店（八佰伴）</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -10731,22 +10773,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台芝罘万达</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -10758,22 +10800,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
         </is>
       </c>
     </row>
@@ -10785,22 +10827,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•无锡八佰伴中心</t>
+          <t>华为智能生活馆•烟台芝罘万达</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10812,22 +10854,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•郑州华联商厦</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
         </is>
       </c>
     </row>
@@ -10839,22 +10881,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴平湖吾悦</t>
+          <t>华为智能生活馆•无锡八佰伴中心</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10866,22 +10908,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>华为智能生活馆•郑州华联商厦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>邵阳市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
+          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
         </is>
       </c>
     </row>
@@ -10893,22 +10935,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•遵义汇川</t>
+          <t>华为智能生活馆•嘉兴平湖吾悦</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>遵义市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10920,20 +10962,74 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>邵阳市</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行授权用户中心•遵义汇川</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>贵州</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>遵义市</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>鸿蒙智行</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
           <t>华为智能生活馆•重庆都市起点购物公园</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>重庆</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>重庆市</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>重庆市涪陵区兴华中路25号泽胜商业步行街都市起点购物公园L1层12/13/14号</t>
         </is>
@@ -11184,7 +11280,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳坂田环城南路服务中心</t>
+          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -11199,7 +11295,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
+          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11307,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>小鹏汽车深圳龙华锦绣科学园服务中心</t>
+          <t>小鹏汽车深圳坂田环城南路服务中心</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -11226,7 +11322,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>广东省深圳市龙华区观湖街道松轩社区虎地排126号锦绣二期4号楼B4层01-26号铺</t>
+          <t>深圳市龙岗区坂田街道环城南路9号高力特智慧能源产业园</t>
         </is>
       </c>
     </row>
@@ -11346,7 +11442,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11361,7 +11457,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11469,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -11388,7 +11484,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
     </row>
@@ -11800,22 +11896,22 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11825,29 +11921,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11857,29 +11953,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11889,14 +11985,14 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -11906,12 +12002,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -11921,7 +12017,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
@@ -11933,17 +12029,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -11953,29 +12049,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -11985,7 +12081,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
@@ -11997,17 +12093,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12017,29 +12113,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12049,29 +12145,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12081,7 +12177,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
@@ -12093,17 +12189,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12113,29 +12209,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12145,29 +12241,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12177,29 +12273,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12209,7 +12305,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
@@ -12221,17 +12317,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12241,29 +12337,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12273,29 +12369,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12305,29 +12401,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12337,29 +12433,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12369,7 +12465,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12381,17 +12477,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12401,29 +12497,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12433,29 +12529,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12465,7 +12561,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
@@ -12504,22 +12600,22 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>沃尔沃</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>天津鲁能城城市中心店</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>天津贵和城市中心店</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12568,22 +12664,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12600,22 +12696,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权钣喷中心（俊汇店）</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>理想汽车铜仁万山授权服务中心（俊汇店）</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12632,22 +12728,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>沃尔沃</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>天津鲁能城城市中心店</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>天津贵和城市中心店</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12696,22 +12792,22 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口北环销售服务中心</t>
+          <t>小米汽车上海松江区松江印象城</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环服务中心</t>
+          <t>小米之家上海市松江区松江印象城汽车体验店</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12721,29 +12817,29 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 88%</t>
+          <t>店名相似度 77%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小米汽车上海松江区松江印象城</t>
+          <t>小鹏汽车周口北环销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小米之家上海市松江区松江印象城汽车体验店</t>
+          <t>小鹏汽车周口南环服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12753,7 +12849,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>店名相似度 77%</t>
+          <t>店名相似度 88%</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260720.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260720.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="品牌总量对比" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="省级网点对比" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（34家）" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新增网点（32家）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="减少网点（28家）" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="变更明细（30条）" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
@@ -719,23 +719,23 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>法拉利</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B12" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>11.1%</t>
+      <c r="C12" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>8626</v>
+        <v>8628</v>
       </c>
       <c r="C19" s="1" t="n">
         <v>8632</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -6507,14 +6507,14 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D267" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="n">
         <v>0</v>
@@ -6528,14 +6528,14 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D268" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C269" s="2" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C270" s="2" t="n">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>重庆</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C271" s="2" t="n">
@@ -6612,59 +6612,59 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D272" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E272" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E273" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>法拉利</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D272" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E272" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D273" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" s="4" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>法拉利</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D274" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E274" s="4" t="n">
-        <v>1</v>
+      <c r="C274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D274" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -10080,7 +10080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10363,54 +10363,54 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>郑州悦骏汽车销售服务有限公司</t>
+          <t>深圳福田卓悦中心体验店L123</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>深圳市</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>如意西路 中国平煤神马集团 郑州 郑东新区</t>
+          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>法拉利</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>沈阳鸿粤鸿福汽车销售服务有限公司</t>
+          <t>茂名茂悦东荟城城市展厅L1-1292</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>沈阳市</t>
+          <t>茂名市</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>浑南区全运路 Shenyang China</t>
+          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
         </is>
       </c>
     </row>
@@ -10422,22 +10422,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>深圳福田卓悦中心体验店L123</t>
+          <t>库尔勒汇嘉时代</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>深圳市</t>
+          <t>巴音郭楞蒙古自治州</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>广东省深圳市福田区福华路与岗厦二路交叉口卓悦中心</t>
+          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
         </is>
       </c>
     </row>
@@ -10449,157 +10449,157 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>茂名茂悦东荟城城市展厅L1-1292</t>
+          <t>莆田城厢万达广场</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>茂名市</t>
+          <t>莆田市</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>广东省茂名市茂南区油城十路与茂名大道交汇处东汇城L1层1292-293、1294-2商铺</t>
+          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>库尔勒汇嘉时代</t>
+          <t>理想汽车芜湖祥盛路零售中心</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>巴音郭楞蒙古自治州</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>新疆维吾尔自治区巴音郭楞蒙古自治州团结辖区朝阳路9库尔勒汇嘉号时代购物中心一楼DJL1006/DJL1007</t>
+          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>莆田城厢万达广场</t>
+          <t>理想汽车江门蓬江临时交付中心</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>莆田市</t>
+          <t>江门市</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>福建省莆田市城厢区荔华东大道8号万达广场F1YX-ZT-002号展位</t>
+          <t>江门市蓬江区建设三路54号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>阿斯顿·马丁</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>理想汽车芜湖祥盛路零售中心</t>
+          <t>阿斯顿·马丁苏州</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>苏州市</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠兹家苑汽车园祥盛路57号</t>
+          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>理想汽车江门蓬江临时交付中心</t>
+          <t>华为授权体验店（宜家荟聚）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>江门市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>江门市蓬江区建设三路54号</t>
+          <t>上海市长宁区金钟路788号01C04A 华为</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>阿斯顿·马丁苏州</t>
+          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>苏州市</t>
+          <t>鄂尔多斯市</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>苏州工业园区苏州大道东418号L101, 江苏省苏州市, 125127</t>
+          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
         </is>
       </c>
     </row>
@@ -10611,22 +10611,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（宜家荟聚）</t>
+          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>眉山市</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>上海市长宁区金钟路788号01C04A 华为</t>
+          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
         </is>
       </c>
     </row>
@@ -10638,22 +10638,22 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•鄂尔多斯铜川汽车园</t>
+          <t>AITO授权用户中心•天津西青大寺汽车园</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>鄂尔多斯市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区铜川镇安居街和兴汽车城3号楼</t>
+          <t>天津市西青区大寺镇储源道17号</t>
         </is>
       </c>
     </row>
@@ -10665,22 +10665,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•眉山眉州大道</t>
+          <t>鸿蒙智行授权用户中心•固原九龙路</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>眉山市</t>
+          <t>固原市</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>四川省眉山市东坡区眉州大道西五段99号1-2层</t>
+          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
         </is>
       </c>
     </row>
@@ -10692,22 +10692,22 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•天津西青大寺汽车园</t>
+          <t>华为授权体验店（八佰伴）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>天津市西青区大寺镇储源道17号</t>
+          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
         </is>
       </c>
     </row>
@@ -10719,22 +10719,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•固原九龙路</t>
+          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>固原市</t>
+          <t>芜湖市</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>宁夏回族自治区固原市原州区九龙路与民族街交叉口</t>
+          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
         </is>
       </c>
     </row>
@@ -10746,22 +10746,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>华为授权体验店（八佰伴）</t>
+          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市镜湖区银湖路八佰伴生活广场3号门一楼华为授权体验店</t>
+          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
         </is>
       </c>
     </row>
@@ -10773,22 +10773,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•芜湖华山路</t>
+          <t>华为智能生活馆•烟台芝罘万达</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>芜湖市</t>
+          <t>烟台市</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>安徽省芜湖市鸠江区九华北路与华山路交叉口</t>
+          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•滨州渤海五路</t>
+          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>肇庆市</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>山东省滨州市滨城区黄河十五路渤海五路北200米路东</t>
+          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
         </is>
       </c>
     </row>
@@ -10827,22 +10827,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•烟台芝罘万达</t>
+          <t>华为智能生活馆•无锡八佰伴中心</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>烟台市</t>
+          <t>无锡市</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>山东省烟台市芝罘区西关南街万达广场一楼华为智能生活馆</t>
+          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10854,22 +10854,22 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•肇庆美轮汽车城</t>
+          <t>华为智能生活馆•郑州华联商厦</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>肇庆市</t>
+          <t>郑州市</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>广东省肇庆市肇庆大道美轮车城北区2号楼</t>
+          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
         </is>
       </c>
     </row>
@@ -10881,22 +10881,22 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•无锡八佰伴中心</t>
+          <t>华为智能生活馆•嘉兴平湖吾悦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>无锡市</t>
+          <t>嘉兴市</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区无锡八佰伴中心1F华为智能生活馆</t>
+          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
         </is>
       </c>
     </row>
@@ -10908,22 +10908,22 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•郑州华联商厦</t>
+          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>郑州市</t>
+          <t>邵阳市</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>河南省郑州市二七区二七路230号郑州华联商厦一层</t>
+          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
         </is>
       </c>
     </row>
@@ -10935,22 +10935,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>华为智能生活馆•嘉兴平湖吾悦</t>
+          <t>鸿蒙智行授权用户中心•遵义汇川</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>嘉兴市</t>
+          <t>遵义市</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市平湖市当湖街道南市路811号吾悦广场1幢1楼1038-1商铺（内街）华为智能生活馆</t>
+          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
         </is>
       </c>
     </row>
@@ -10962,74 +10962,20 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•邵阳世纪大道</t>
+          <t>华为智能生活馆•重庆都市起点购物公园</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>重庆</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>邵阳市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>湖南省邵阳市双清区邵阳大道东联接线交叉口天骄汽配城内东100米</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行授权用户中心•遵义汇川</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>遵义市</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>贵州省遵义市汇川区董公寺街道和平社区汽车商贸城通源汽车文化广场内（临时营业）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>鸿蒙智行</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>华为智能生活馆•重庆都市起点购物公园</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>重庆市</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>重庆市涪陵区兴华中路25号泽胜商业步行街都市起点购物公园L1层12/13/14号</t>
         </is>
@@ -11442,7 +11388,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>福州建发众驰4S中心</t>
+          <t>福州建发捷路4S中心</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -11457,7 +11403,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市闽侯县上街镇源通东路63号</t>
+          <t>福建省福州市马尾区马尾镇马江路28号</t>
         </is>
       </c>
     </row>
@@ -11469,7 +11415,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>福州建发捷路4S中心</t>
+          <t>福州建发众驰4S中心</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -11484,7 +11430,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>福建省福州市马尾区马尾镇马江路28号</t>
+          <t>福建省福州市闽侯县上街镇源通东路63号</t>
         </is>
       </c>
     </row>
@@ -11901,17 +11847,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>杭州滨江银泰体验店</t>
+          <t>成都银泰中心IN99</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11921,29 +11867,29 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
+          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•余慈鑫时代</t>
+          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11953,29 +11899,29 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
+          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
+          <t>成都仁和新城城市展厅F1-LS-02</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11985,7 +11931,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
+          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
         </is>
       </c>
     </row>
@@ -12002,12 +11948,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮安香港路销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12017,29 +11963,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
+          <t>扬州京华城</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12049,29 +11995,29 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
+          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•南宁云景路</t>
+          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12081,7 +12027,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
+          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
         </is>
       </c>
     </row>
@@ -12093,17 +12039,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天津空港销售服务中心</t>
+          <t>小鹏汽车淮安香港路销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12113,29 +12059,29 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
+          <t>淮安市淮阴区钱江路 100 号 → 江苏省淮安市淮阴区钱江路100号</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>小米</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
+          <t>小鹏汽车济南华山环宇城销售中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12145,29 +12091,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
+          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>AITO授权用户中心•余慈鑫时代</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12177,7 +12123,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心</t>
+          <t>慈溪市横河镇前应路1176号 → 浙江省慈溪市横河镇前应路1176号</t>
         </is>
       </c>
     </row>
@@ -12189,17 +12135,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车常德湘西北汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12209,29 +12155,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>常德市武陵区常德大道龙港路1088号（湘西北汽车城内） → 湖南省常德市武陵区龙港北路小鹏汽车二楼（湘西北汽车城内）</t>
+          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>特斯拉</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>杭州滨江银泰体验店</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12241,29 +12187,29 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区白云街1号万国汽配城后 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>浙江省杭州市滨江区西兴街道启智街475号商业广场1层134号 → 浙江省杭州市滨江区滨和路598号滨江银泰A区8号门入口</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>扬州京华城</t>
+          <t>AITO授权用户中心•贵阳华通汽车城</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12273,29 +12219,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04 → 江苏省扬州市邗江区京华城路168号京华城1F南通道GSIL1S04</t>
+          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>成都银泰中心IN99</t>
+          <t>鸿蒙智行尚界用户中心•惠州惠博大道</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12305,14 +12251,14 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位 → 四川省成都市高新区天府大道1199号成都银泰中心in99店L1层L101c号铺位</t>
+          <t>广东省惠州市江北西区7号小区D1（金山汽车城内） → 广东省惠州市惠城区惠博大道江北西部7号小区金山汽车城3街1号B展场</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -12322,12 +12268,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潮州潮汕路销售服务中心</t>
+          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12337,7 +12283,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
+          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
         </is>
       </c>
     </row>
@@ -12349,17 +12295,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•梅州梅塘东路</t>
+          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12369,29 +12315,29 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>广东省梅州市梅江区梅塘东路30号 → 广东省梅州市梅江区三角镇梅塘东路30号</t>
+          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>理想汽车成都合生汇零售中心</t>
+          <t>小鹏汽车潮州潮汕路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12401,29 +12347,29 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
+          <t>广东省潮安区潮汕公路乌洋路段 → 广东省潮州市潮汕公路乌洋路段</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AITO授权用户中心•贵阳华通汽车城</t>
+          <t>小米之家山东省烟台市芝罘区烟台大悦城汽车体验店</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12433,29 +12379,29 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>贵州省贵阳市云岩区金阳南路118号华通汽车城（临时营业） → 贵州省贵阳市云岩区金阳南路118号</t>
+          <t>北马路150号大悦城广场1层1F-30 → 山东省烟台市芝罘区北马路150号大悦城1F30号</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车伊犁中亚汽车城销售服务中心</t>
+          <t>理想汽车成都合生汇零售中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12465,29 +12411,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>新疆伊宁市巴彦岱中亚汽车博览中心中央二号展厅 → 新疆伊宁市巴彦岱城投汽车产业园</t>
+          <t>成都市温江区光华大道三段1588号3栋1F层L1-02号 → 成都市温江区光华大道三段1588号合生汇商场1F层3号门外（星巴克旁，光华公园地铁G2出口旁）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>小米</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车济南华山环宇城销售中心</t>
+          <t>小米之家广东省广州市增城区增城万达汽车体验店</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12497,29 +12443,29 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>济南市历城区将军路华山环宇城购物中心1层L152;153A;153B单元 → 济南市历城区将军路华山环宇城购物中心1层L129；130单元</t>
+          <t>增城大道69号 → 增城大道69号增城万达广场1061，1062，1063</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>特斯拉</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>成都仁和新城城市展厅F1-LS-02</t>
+          <t>鸿蒙智行授权用户中心•南宁云景路</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12529,29 +12475,29 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>四川省成都市四川省成都市府城大道西段505号1层LS-02铺位 → 四川省成都市武侯区府城大道西段505号1层LS-02铺位</t>
+          <t>广西壮族自治区南宁市兴宁区三塘北路三塘派出所西南侧约60米（临时营业） → 广西壮族自治区南宁市兴宁区三塘镇兴工北路汽车市场17-27号（临时营业）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•嘉兴南溪东路</t>
+          <t>小鹏汽车天津空港销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12561,7 +12507,7 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市南湖区大桥镇南溪东路1362号0003幢（临时营业） → 浙江省嘉兴市南湖区南溪东路1362号</t>
+          <t>天津市滨海新区空港经济区环河北路62号 → 天津市东丽区空港经济区环河北路62号</t>
         </is>
       </c>
     </row>
@@ -12632,22 +12578,22 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>理想</t>
+          <t>奔驰</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车鹿城零售中心</t>
+          <t>宜春华宏臻汽车有限公司</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>理想汽车温州鹿城零售中心</t>
+          <t>宜春华宏星汽车有限公司</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12696,22 +12642,22 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>理想</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
+          <t>理想汽车鹿城零售中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
+          <t>理想汽车温州鹿城零售中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12728,22 +12674,22 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>奔驰</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏臻汽车有限公司</t>
+          <t>鸿蒙智行尚界用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>宜春华宏星汽车有限公司</t>
+          <t>鸿蒙智行授权用户中心•三明北汽车城</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
